--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M22B1_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M22B1_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>33.37</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="30">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>62.53</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>55.1698</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>52.9056</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>95.9</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>2.2642</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2123,11 +2123,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>55.1772</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2246,6 +2246,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2378,6 +2379,7 @@
       <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="17" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2424,6 +2426,7 @@
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="96" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2808,11 +2811,11 @@
       </c>
       <c r="B17" s="33">
         <f>SUM(B10:B16)</f>
-        <v/>
+        <v>273.96</v>
       </c>
       <c r="C17" s="23">
         <f>SUM(C10:C16)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -2822,19 +2825,19 @@
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17">
         <f>ROUND(AVERAGE(F10:F16),2)</f>
-        <v/>
+        <v>29.26</v>
       </c>
       <c r="G17" s="22">
         <f>ROUND(AVERAGE(G10:G16),4)</f>
-        <v/>
+        <v>0.5792</v>
       </c>
       <c r="H17" s="23">
         <f>ROUND(AVERAGE(H10:H16),2)</f>
-        <v/>
+        <v>90.14</v>
       </c>
       <c r="I17" s="23">
         <f>ROUND(AVERAGE(I10:I16),2)</f>
-        <v/>
+        <v>14.61</v>
       </c>
     </row>
     <row r="18"/>
